--- a/data_group/matriz_contrastes_pwpm_temp.xlsx
+++ b/data_group/matriz_contrastes_pwpm_temp.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="442">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -140,895 +140,1204 @@
     <t xml:space="preserve">PF...1</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0009</t>
+    <t xml:space="preserve">26.046907</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;.0001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0770</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4</t>
+    <t xml:space="preserve">25.826454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.688023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.601703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.538685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.509208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.442080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.375321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.315384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.910356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF_early...2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.1663001870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.880607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7396</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0081014472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.818353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.097443809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.785467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2772</t>
   </si>
   <si>
     <t xml:space="preserve">0.0017</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF_early...2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.1609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9992</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.000911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.15731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.26289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.698</t>
+    <t xml:space="preserve">-0.087394752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.689098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.10913621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.647822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1596417420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.668850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.206232528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.648313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.235397454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.020237573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.335622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.621106101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.531462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0036</t>
   </si>
   <si>
     <t xml:space="preserve">SF_intermediate...3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 0.1986</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.043123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.044034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.16162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1545</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.27000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.498</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999</t>
+    <t xml:space="preserve"> 0.1991894595</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0328892725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.847718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0449762403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0530776875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.871431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.157980867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.060537058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.846004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.198044936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.110650184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.799748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.21100162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.10186541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.749687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1665280022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0068862603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.675736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.169173535</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.037058993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.611254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.263130165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.027732712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.638451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.146339670</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.126102097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.461724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.404941925</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.216164176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.315298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9195</t>
   </si>
   <si>
     <t xml:space="preserve">SF_advanced...4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 0.1670</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.114637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.115547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.071513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.25822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.10091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.09660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.28058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.389</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.309</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.109</t>
+    <t xml:space="preserve"> 0.1938159986</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0275158116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0053734609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.853091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0958852369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1039866841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0509089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.922339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.222166357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.124722547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.064185490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.910189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.281098069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.193703317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.083053133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.882801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.31480017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.20566396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.10379855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.853486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2558814325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0962396905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0893534303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.765089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.245289864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.039057336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.076116329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.687370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.286429692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.051032239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.023299527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.661750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.254395274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.234157702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.108055605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.569779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.353227206</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.267878894</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.051714718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.263584</t>
   </si>
   <si>
     <t xml:space="preserve">PF...5</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5</t>
+    <t xml:space="preserve">25.548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.508</t>
   </si>
   <si>
     <t xml:space="preserve">SF_early...6</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.31134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.37596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.26783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.23435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.4120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.8165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0689</t>
+    <t xml:space="preserve">-0.3076028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3750001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3981327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3658707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2597782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2223400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2694913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.335748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.393241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.835443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0019</t>
   </si>
   <si>
     <t xml:space="preserve">SF_intermediate...7</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.30822</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.00312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.39664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.02068</t>
+    <t xml:space="preserve">-0.3040112</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0035916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3826284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0076283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3912831</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0068496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3740196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0081489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2881296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0283513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2318775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0095375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2781753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0086840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.334676</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.001072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.345253</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.047988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.726794</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.108649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF_advanced...8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3209573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0169461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3923339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0173338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0097056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3707329</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0273998</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0205502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3490070</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0168637</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0250126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2570185</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0027598</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0311111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2149527</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0073873</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0169248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2639808</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0055105</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0141945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.299066</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.035610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.320689</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.072552</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.024564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.663107</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.172337</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.063687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PF...9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF_early...10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5949399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.864</t>
   </si>
   <si>
     <t xml:space="preserve">0.9951</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.4116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.30692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.03909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.25669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.02234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8770</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3738</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.7603</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF_advanced...8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.33912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.02777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.03090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.40282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.02686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3763</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0232</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3541</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0156</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.27221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00438</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.03471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.23102</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.00333</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.02567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2810</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3159</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0306</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3394</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0726</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.6680</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.1485</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PF...9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF_early...10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.5880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.452717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.3438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0380</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.17157</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.1303</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.1672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5139</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.13683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8070</t>
+    <t xml:space="preserve">0.1365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.4625016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3441332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.218511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.219</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.204749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.081</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.186929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.983</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.221674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.838</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.154707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.796</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.045902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1961</t>
   </si>
   <si>
     <t xml:space="preserve">SF_intermediate...11</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.5456</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.533649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.080932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.5047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.05504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.22661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1952</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.00145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.13538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1335</t>
+    <t xml:space="preserve">-0.5870711</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0078688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5707117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1082100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5340318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1898985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.429951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.211440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.209055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.179026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.043353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.248102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.043508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.230437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.012808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.234482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.004369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.159076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.181623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.227526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.772</t>
   </si>
   <si>
     <t xml:space="preserve">SF_advanced...12</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.5075</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0805</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.533435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.000213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.4851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1414</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.1918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.05971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.23127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.2014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0230</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.1225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0447</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.1505</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.02690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.10993</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.02545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0402</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0291</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.1625</t>
+    <t xml:space="preserve">-0.5316648</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0632752</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0554063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5682438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1057422</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0024678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5255288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1813956</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0085029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.470216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.251705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.040265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.275175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.245145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.066119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.096962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.301711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.053609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.134750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.321679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.091242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.304</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.092299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.129375</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.105107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.968</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.011400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.143307</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.015769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.042500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.088402</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.139124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.633</t>
   </si>
 </sst>
 </file>
@@ -1493,141 +1802,141 @@
         <v>43</v>
       </c>
       <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
         <v>44</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>45</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>46</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>47</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>48</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>49</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" t="s">
         <v>50</v>
       </c>
-      <c r="K2" t="s">
+      <c r="O2" t="s">
         <v>51</v>
       </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" t="s">
         <v>52</v>
       </c>
-      <c r="M2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="S2" t="s">
         <v>53</v>
       </c>
-      <c r="O2" t="s">
+      <c r="T2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" t="s">
         <v>54</v>
       </c>
-      <c r="P2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="W2" t="s">
         <v>55</v>
       </c>
-      <c r="S2" t="s">
+      <c r="X2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z2" t="s">
         <v>56</v>
       </c>
-      <c r="T2" t="s">
-        <v>44</v>
-      </c>
-      <c r="U2" t="s">
-        <v>44</v>
-      </c>
-      <c r="V2" t="s">
-        <v>55</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="AA2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD2" t="s">
         <v>57</v>
       </c>
-      <c r="X2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AE2" t="s">
         <v>58</v>
       </c>
-      <c r="AA2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AF2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH2" t="s">
         <v>59</v>
       </c>
-      <c r="AC2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>60</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL2" t="s">
         <v>61</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>62</v>
-      </c>
       <c r="AM2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AN2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AO2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>64</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>65</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>66</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>67</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>68</v>
-      </c>
-      <c r="G3" t="s">
-        <v>46</v>
       </c>
       <c r="H3" t="s">
         <v>69</v>
@@ -1639,1347 +1948,1347 @@
         <v>71</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="L3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O3" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="P3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q3" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="R3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="T3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W3" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="X3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Y3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="AB3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AC3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AD3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AE3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="AF3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AH3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="AJ3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AK3" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="AL3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="AM3" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="AN3" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="AO3" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="G4" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="I4" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="J4" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="K4" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L4" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="M4" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="N4" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="O4" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="Q4" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="R4" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="S4" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="T4" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="U4" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="V4" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="W4" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="X4" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="Y4" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="Z4" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="AA4" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="AB4" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="AC4" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="AD4" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="AE4" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AF4" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="AG4" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="AH4" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="AI4" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="AJ4" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="AK4" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="AL4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="AM4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="AN4" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="AO4" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="F5" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="G5" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="H5" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="I5" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="J5" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="K5" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="L5" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="M5" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="N5" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="O5" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="P5" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="Q5" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="R5" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="S5" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="T5" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="U5" t="s">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="V5" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="W5" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="X5" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="Y5" t="s">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="Z5" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="AA5" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB5" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="AC5" t="s">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="AD5" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="AE5" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="AF5" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="AG5" t="s">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="AH5" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="AI5" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="AJ5" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="AK5" t="s">
-        <v>53</v>
+        <v>178</v>
       </c>
       <c r="AL5" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="AM5" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="AN5" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="AO5" t="s">
-        <v>60</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>184</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="K6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="O6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R6" t="s">
-        <v>60</v>
+        <v>188</v>
       </c>
       <c r="S6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V6" t="s">
-        <v>58</v>
+        <v>189</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Y6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z6" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AB6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AD6" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="AE6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AF6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH6" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="AI6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AJ6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AL6" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="AM6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AN6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AO6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="E7" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="F7" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="H7" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="I7" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="J7" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="K7" t="s">
-        <v>50</v>
+        <v>204</v>
       </c>
       <c r="L7" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="M7" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="N7" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="O7" t="s">
-        <v>50</v>
+        <v>208</v>
       </c>
       <c r="P7" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="Q7" t="s">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="R7" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="S7" t="s">
-        <v>53</v>
+        <v>212</v>
       </c>
       <c r="T7" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="U7" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="V7" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="W7" t="s">
-        <v>53</v>
+        <v>216</v>
       </c>
       <c r="X7" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="Y7" t="s">
-        <v>67</v>
+        <v>218</v>
       </c>
       <c r="Z7" t="s">
-        <v>176</v>
+        <v>219</v>
       </c>
       <c r="AA7" t="s">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AB7" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="AC7" t="s">
-        <v>47</v>
+        <v>222</v>
       </c>
       <c r="AD7" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="AE7" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="AF7" t="s">
-        <v>179</v>
+        <v>225</v>
       </c>
       <c r="AG7" t="s">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c r="AH7" t="s">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="AI7" t="s">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="AJ7" t="s">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="AK7" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="AL7" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="AM7" t="s">
-        <v>60</v>
+        <v>232</v>
       </c>
       <c r="AN7" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="AO7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="C8" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>237</v>
       </c>
       <c r="E8" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="F8" t="s">
-        <v>190</v>
+        <v>239</v>
       </c>
       <c r="G8" t="s">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>241</v>
       </c>
       <c r="I8" t="s">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="J8" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="K8" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="L8" t="s">
-        <v>50</v>
+        <v>245</v>
       </c>
       <c r="M8" t="s">
-        <v>195</v>
+        <v>246</v>
       </c>
       <c r="N8" t="s">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="O8" t="s">
-        <v>197</v>
+        <v>248</v>
       </c>
       <c r="P8" t="s">
-        <v>50</v>
+        <v>249</v>
       </c>
       <c r="Q8" t="s">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="R8" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
       <c r="S8" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="T8" t="s">
-        <v>50</v>
+        <v>253</v>
       </c>
       <c r="U8" t="s">
-        <v>201</v>
+        <v>254</v>
       </c>
       <c r="V8" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="W8" t="s">
-        <v>203</v>
+        <v>256</v>
       </c>
       <c r="X8" t="s">
-        <v>53</v>
+        <v>257</v>
       </c>
       <c r="Y8" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="Z8" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="AA8" t="s">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="AB8" t="s">
-        <v>55</v>
+        <v>261</v>
       </c>
       <c r="AC8" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="AD8" t="s">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="AE8" t="s">
-        <v>209</v>
+        <v>264</v>
       </c>
       <c r="AF8" t="s">
-        <v>55</v>
+        <v>265</v>
       </c>
       <c r="AG8" t="s">
-        <v>210</v>
+        <v>266</v>
       </c>
       <c r="AH8" t="s">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="AI8" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="AJ8" t="s">
-        <v>58</v>
+        <v>269</v>
       </c>
       <c r="AK8" t="s">
-        <v>213</v>
+        <v>270</v>
       </c>
       <c r="AL8" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="AM8" t="s">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="AN8" t="s">
-        <v>60</v>
+        <v>273</v>
       </c>
       <c r="AO8" t="s">
-        <v>216</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="B9" t="s">
-        <v>218</v>
+        <v>276</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>277</v>
       </c>
       <c r="D9" t="s">
-        <v>220</v>
+        <v>278</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>279</v>
       </c>
       <c r="F9" t="s">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="G9" t="s">
-        <v>222</v>
+        <v>281</v>
       </c>
       <c r="H9" t="s">
-        <v>223</v>
+        <v>282</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>283</v>
       </c>
       <c r="J9" t="s">
-        <v>224</v>
+        <v>284</v>
       </c>
       <c r="K9" t="s">
-        <v>225</v>
+        <v>285</v>
       </c>
       <c r="L9" t="s">
-        <v>226</v>
+        <v>286</v>
       </c>
       <c r="M9" t="s">
-        <v>50</v>
+        <v>287</v>
       </c>
       <c r="N9" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="O9" t="s">
-        <v>228</v>
+        <v>289</v>
       </c>
       <c r="P9" t="s">
-        <v>229</v>
+        <v>290</v>
       </c>
       <c r="Q9" t="s">
-        <v>50</v>
+        <v>291</v>
       </c>
       <c r="R9" t="s">
-        <v>230</v>
+        <v>292</v>
       </c>
       <c r="S9" t="s">
-        <v>231</v>
+        <v>293</v>
       </c>
       <c r="T9" t="s">
-        <v>232</v>
+        <v>294</v>
       </c>
       <c r="U9" t="s">
-        <v>53</v>
+        <v>295</v>
       </c>
       <c r="V9" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="W9" t="s">
-        <v>234</v>
+        <v>297</v>
       </c>
       <c r="X9" t="s">
-        <v>235</v>
+        <v>298</v>
       </c>
       <c r="Y9" t="s">
-        <v>53</v>
+        <v>299</v>
       </c>
       <c r="Z9" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="AA9" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="AB9" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="AC9" t="s">
-        <v>55</v>
+        <v>303</v>
       </c>
       <c r="AD9" t="s">
-        <v>239</v>
+        <v>304</v>
       </c>
       <c r="AE9" t="s">
-        <v>240</v>
+        <v>305</v>
       </c>
       <c r="AF9" t="s">
-        <v>241</v>
+        <v>306</v>
       </c>
       <c r="AG9" t="s">
-        <v>58</v>
+        <v>307</v>
       </c>
       <c r="AH9" t="s">
-        <v>242</v>
+        <v>308</v>
       </c>
       <c r="AI9" t="s">
-        <v>243</v>
+        <v>309</v>
       </c>
       <c r="AJ9" t="s">
-        <v>244</v>
+        <v>310</v>
       </c>
       <c r="AK9" t="s">
-        <v>60</v>
+        <v>311</v>
       </c>
       <c r="AL9" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
       <c r="AM9" t="s">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="AN9" t="s">
-        <v>247</v>
+        <v>314</v>
       </c>
       <c r="AO9" t="s">
-        <v>154</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>316</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>317</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>154</v>
+        <v>318</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J10" t="s">
-        <v>155</v>
+        <v>319</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N10" t="s">
-        <v>155</v>
+        <v>320</v>
       </c>
       <c r="O10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R10" t="s">
-        <v>154</v>
+        <v>321</v>
       </c>
       <c r="S10" t="s">
-        <v>249</v>
+        <v>322</v>
       </c>
       <c r="T10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V10" t="s">
-        <v>60</v>
+        <v>323</v>
       </c>
       <c r="W10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X10" t="s">
-        <v>250</v>
+        <v>324</v>
       </c>
       <c r="Y10" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
       <c r="Z10" t="s">
-        <v>154</v>
+        <v>326</v>
       </c>
       <c r="AA10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AB10" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="AC10" t="s">
-        <v>253</v>
+        <v>328</v>
       </c>
       <c r="AD10" t="s">
-        <v>155</v>
+        <v>329</v>
       </c>
       <c r="AE10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AF10" t="s">
-        <v>254</v>
+        <v>330</v>
       </c>
       <c r="AG10" t="s">
-        <v>255</v>
+        <v>331</v>
       </c>
       <c r="AH10" t="s">
-        <v>62</v>
+        <v>332</v>
       </c>
       <c r="AI10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AJ10" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="AK10" t="s">
-        <v>256</v>
+        <v>333</v>
       </c>
       <c r="AL10" t="s">
-        <v>257</v>
+        <v>334</v>
       </c>
       <c r="AM10" t="s">
-        <v>258</v>
+        <v>335</v>
       </c>
       <c r="AN10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AO10" t="s">
-        <v>259</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>260</v>
+        <v>337</v>
       </c>
       <c r="B11" t="s">
-        <v>261</v>
+        <v>338</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>339</v>
       </c>
       <c r="D11" t="s">
-        <v>262</v>
+        <v>340</v>
       </c>
       <c r="E11" t="s">
-        <v>263</v>
+        <v>341</v>
       </c>
       <c r="F11" t="s">
-        <v>264</v>
+        <v>342</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>343</v>
       </c>
       <c r="H11" t="s">
-        <v>265</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
-        <v>266</v>
+        <v>344</v>
       </c>
       <c r="J11" t="s">
-        <v>267</v>
+        <v>345</v>
       </c>
       <c r="K11" t="s">
-        <v>55</v>
+        <v>346</v>
       </c>
       <c r="L11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N11" t="s">
-        <v>268</v>
+        <v>347</v>
       </c>
       <c r="O11" t="s">
-        <v>60</v>
+        <v>348</v>
       </c>
       <c r="P11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R11" t="s">
-        <v>269</v>
+        <v>349</v>
       </c>
       <c r="S11" t="s">
-        <v>154</v>
+        <v>350</v>
       </c>
       <c r="T11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V11" t="s">
-        <v>270</v>
+        <v>351</v>
       </c>
       <c r="W11" t="s">
-        <v>155</v>
+        <v>352</v>
       </c>
       <c r="X11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Y11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z11" t="s">
-        <v>271</v>
+        <v>353</v>
       </c>
       <c r="AA11" t="s">
-        <v>156</v>
+        <v>354</v>
       </c>
       <c r="AB11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AD11" t="s">
-        <v>272</v>
+        <v>355</v>
       </c>
       <c r="AE11" t="s">
-        <v>62</v>
+        <v>356</v>
       </c>
       <c r="AF11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG11" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
       <c r="AH11" t="s">
-        <v>274</v>
+        <v>357</v>
       </c>
       <c r="AI11" t="s">
-        <v>275</v>
+        <v>358</v>
       </c>
       <c r="AJ11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK11" t="s">
-        <v>276</v>
+        <v>47</v>
       </c>
       <c r="AL11" t="s">
-        <v>277</v>
+        <v>359</v>
       </c>
       <c r="AM11" t="s">
-        <v>278</v>
+        <v>360</v>
       </c>
       <c r="AN11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AO11" t="s">
-        <v>279</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>280</v>
+        <v>362</v>
       </c>
       <c r="B12" t="s">
-        <v>281</v>
+        <v>363</v>
       </c>
       <c r="C12" t="s">
-        <v>282</v>
+        <v>364</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>365</v>
       </c>
       <c r="E12" t="s">
-        <v>283</v>
+        <v>366</v>
       </c>
       <c r="F12" t="s">
-        <v>284</v>
+        <v>367</v>
       </c>
       <c r="G12" t="s">
-        <v>285</v>
+        <v>368</v>
       </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>369</v>
       </c>
       <c r="I12" t="s">
-        <v>47</v>
+        <v>225</v>
       </c>
       <c r="J12" t="s">
-        <v>286</v>
+        <v>370</v>
       </c>
       <c r="K12" t="s">
-        <v>287</v>
+        <v>371</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>372</v>
       </c>
       <c r="M12" t="s">
-        <v>288</v>
+        <v>373</v>
       </c>
       <c r="N12" t="s">
-        <v>289</v>
+        <v>374</v>
       </c>
       <c r="O12" t="s">
-        <v>290</v>
+        <v>375</v>
       </c>
       <c r="P12" t="s">
-        <v>55</v>
+        <v>376</v>
       </c>
       <c r="Q12" t="s">
-        <v>291</v>
+        <v>377</v>
       </c>
       <c r="R12" t="s">
-        <v>292</v>
+        <v>378</v>
       </c>
       <c r="S12" t="s">
-        <v>293</v>
+        <v>379</v>
       </c>
       <c r="T12" t="s">
-        <v>58</v>
+        <v>380</v>
       </c>
       <c r="U12" t="s">
-        <v>294</v>
+        <v>381</v>
       </c>
       <c r="V12" t="s">
-        <v>295</v>
+        <v>382</v>
       </c>
       <c r="W12" t="s">
-        <v>296</v>
+        <v>383</v>
       </c>
       <c r="X12" t="s">
-        <v>60</v>
+        <v>384</v>
       </c>
       <c r="Y12" t="s">
-        <v>297</v>
+        <v>385</v>
       </c>
       <c r="Z12" t="s">
-        <v>298</v>
+        <v>386</v>
       </c>
       <c r="AA12" t="s">
-        <v>299</v>
+        <v>387</v>
       </c>
       <c r="AB12" t="s">
-        <v>154</v>
+        <v>388</v>
       </c>
       <c r="AC12" t="s">
-        <v>300</v>
+        <v>389</v>
       </c>
       <c r="AD12" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="AE12" t="s">
-        <v>302</v>
+        <v>391</v>
       </c>
       <c r="AF12" t="s">
-        <v>155</v>
+        <v>392</v>
       </c>
       <c r="AG12" t="s">
-        <v>44</v>
+        <v>393</v>
       </c>
       <c r="AH12" t="s">
-        <v>303</v>
+        <v>394</v>
       </c>
       <c r="AI12" t="s">
-        <v>304</v>
+        <v>395</v>
       </c>
       <c r="AJ12" t="s">
-        <v>62</v>
+        <v>396</v>
       </c>
       <c r="AK12" t="s">
-        <v>305</v>
+        <v>397</v>
       </c>
       <c r="AL12" t="s">
-        <v>306</v>
+        <v>398</v>
       </c>
       <c r="AM12" t="s">
-        <v>307</v>
+        <v>399</v>
       </c>
       <c r="AN12" t="s">
-        <v>275</v>
+        <v>400</v>
       </c>
       <c r="AO12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>308</v>
+        <v>401</v>
       </c>
       <c r="B13" t="s">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="C13" t="s">
-        <v>310</v>
+        <v>403</v>
       </c>
       <c r="D13" t="s">
-        <v>311</v>
+        <v>404</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>405</v>
       </c>
       <c r="F13" t="s">
-        <v>312</v>
+        <v>406</v>
       </c>
       <c r="G13" t="s">
-        <v>313</v>
+        <v>407</v>
       </c>
       <c r="H13" t="s">
-        <v>314</v>
+        <v>408</v>
       </c>
       <c r="I13" t="s">
-        <v>50</v>
+        <v>409</v>
       </c>
       <c r="J13" t="s">
-        <v>315</v>
+        <v>410</v>
       </c>
       <c r="K13" t="s">
-        <v>316</v>
+        <v>411</v>
       </c>
       <c r="L13" t="s">
-        <v>317</v>
+        <v>412</v>
       </c>
       <c r="M13" t="s">
-        <v>53</v>
+        <v>413</v>
       </c>
       <c r="N13" t="s">
-        <v>318</v>
+        <v>414</v>
       </c>
       <c r="O13" t="s">
-        <v>319</v>
+        <v>415</v>
       </c>
       <c r="P13" t="s">
-        <v>320</v>
+        <v>416</v>
       </c>
       <c r="Q13" t="s">
-        <v>55</v>
+        <v>417</v>
       </c>
       <c r="R13" t="s">
-        <v>321</v>
+        <v>418</v>
       </c>
       <c r="S13" t="s">
-        <v>322</v>
+        <v>419</v>
       </c>
       <c r="T13" t="s">
-        <v>323</v>
+        <v>420</v>
       </c>
       <c r="U13" t="s">
-        <v>58</v>
+        <v>421</v>
       </c>
       <c r="V13" t="s">
-        <v>324</v>
+        <v>422</v>
       </c>
       <c r="W13" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="X13" t="s">
-        <v>326</v>
+        <v>424</v>
       </c>
       <c r="Y13" t="s">
-        <v>60</v>
+        <v>425</v>
       </c>
       <c r="Z13" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
       <c r="AA13" t="s">
-        <v>328</v>
+        <v>427</v>
       </c>
       <c r="AB13" t="s">
-        <v>329</v>
+        <v>428</v>
       </c>
       <c r="AC13" t="s">
-        <v>154</v>
+        <v>429</v>
       </c>
       <c r="AD13" t="s">
-        <v>330</v>
+        <v>430</v>
       </c>
       <c r="AE13" t="s">
-        <v>331</v>
+        <v>431</v>
       </c>
       <c r="AF13" t="s">
-        <v>332</v>
+        <v>432</v>
       </c>
       <c r="AG13" t="s">
-        <v>62</v>
+        <v>433</v>
       </c>
       <c r="AH13" t="s">
-        <v>333</v>
+        <v>434</v>
       </c>
       <c r="AI13" t="s">
-        <v>334</v>
+        <v>435</v>
       </c>
       <c r="AJ13" t="s">
-        <v>335</v>
+        <v>436</v>
       </c>
       <c r="AK13" t="s">
-        <v>62</v>
+        <v>437</v>
       </c>
       <c r="AL13" t="s">
-        <v>336</v>
+        <v>438</v>
       </c>
       <c r="AM13" t="s">
-        <v>337</v>
+        <v>439</v>
       </c>
       <c r="AN13" t="s">
-        <v>338</v>
+        <v>440</v>
       </c>
       <c r="AO13" t="s">
-        <v>257</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
